--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93361</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045276</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87547</v>
+        <v>87548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136044529</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136044589</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136044683</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136045265</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136045306</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87548</v>
+        <v>87549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045276</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87549</v>
+        <v>87550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136044529</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136044589</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136044683</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136045265</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136045306</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136044914</v>
       </c>
       <c r="B11" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136044779</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045276</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87550</v>
+        <v>87556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136044529</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136044589</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136044683</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136045265</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136045306</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136044914</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136044779</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045276</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87556</v>
+        <v>87557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136044529</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136044589</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136044683</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136045265</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136045306</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136044914</v>
       </c>
       <c r="B11" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136044779</v>
       </c>
       <c r="B12" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045276</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87557</v>
+        <v>87563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136044529</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136044589</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136044683</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136045265</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136045306</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045276</v>
       </c>
       <c r="B2" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87563</v>
+        <v>87570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136044529</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136044589</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136044683</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136045265</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136045306</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136044914</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136044779</v>
       </c>
       <c r="B12" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045276</v>
       </c>
       <c r="B2" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136044529</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136044589</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136044683</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136045265</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136045306</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136044914</v>
       </c>
       <c r="B11" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136044779</v>
       </c>
       <c r="B12" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045276</v>
       </c>
       <c r="B2" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87583</v>
+        <v>87584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136044529</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136044589</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136044683</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136045265</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136045306</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
